--- a/Documentation/Development/MediaAssetsList.xlsx
+++ b/Documentation/Development/MediaAssetsList.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30461751\Desktop\EarthShard\Documentation\Development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE54DD89-021D-4D44-B431-EBF6D8B41EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336329A6-6FB9-4293-B1F3-0D15A90F362F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9855" yWindow="0" windowWidth="28545" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40485" yWindow="1080" windowWidth="28545" windowHeight="18240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MainMenu" sheetId="1" r:id="rId1"/>
+    <sheet name="Level1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="102">
   <si>
     <t>Asset name</t>
   </si>
@@ -40,13 +41,304 @@
   </si>
   <si>
     <t>Asset Count</t>
+  </si>
+  <si>
+    <t>non-static</t>
+  </si>
+  <si>
+    <t>2. Winds of Valor</t>
+  </si>
+  <si>
+    <t>.wav</t>
+  </si>
+  <si>
+    <t>Main Camera</t>
+  </si>
+  <si>
+    <t>animation</t>
+  </si>
+  <si>
+    <t>animated camera movement in menu</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>title @4x</t>
+  </si>
+  <si>
+    <t>.png</t>
+  </si>
+  <si>
+    <t>game title</t>
+  </si>
+  <si>
+    <t>Button (shadow)</t>
+  </si>
+  <si>
+    <t>button texture and for backgrounds</t>
+  </si>
+  <si>
+    <t>Malevoment crow logo 1</t>
+  </si>
+  <si>
+    <t>Developer logo</t>
+  </si>
+  <si>
+    <t>SM_Env_Dust_04</t>
+  </si>
+  <si>
+    <t>.fbx</t>
+  </si>
+  <si>
+    <t>sand asset</t>
+  </si>
+  <si>
+    <t>static</t>
+  </si>
+  <si>
+    <t>Mountain_desert_009</t>
+  </si>
+  <si>
+    <t>mountain asset</t>
+  </si>
+  <si>
+    <t>Mountain_desert_006</t>
+  </si>
+  <si>
+    <t>Mountain_desert_002</t>
+  </si>
+  <si>
+    <t>Mountain_desert_003</t>
+  </si>
+  <si>
+    <t>Mountain_desert_005</t>
+  </si>
+  <si>
+    <t>Mountain_desert_008</t>
+  </si>
+  <si>
+    <t>Plateau_desert_004</t>
+  </si>
+  <si>
+    <t>Plateau_desert_002</t>
+  </si>
+  <si>
+    <t>Assets_Campfire</t>
+  </si>
+  <si>
+    <t>campfire asset</t>
+  </si>
+  <si>
+    <t>fire01</t>
+  </si>
+  <si>
+    <t>particle</t>
+  </si>
+  <si>
+    <t>campfire flame and smoke</t>
+  </si>
+  <si>
+    <t>SM_Env_Bramble_03</t>
+  </si>
+  <si>
+    <t>foliage</t>
+  </si>
+  <si>
+    <t>SM_Env_Bramble_02</t>
+  </si>
+  <si>
+    <t>SM_Env_Bramble_01</t>
+  </si>
+  <si>
+    <t>SM_Env_Dust_01</t>
+  </si>
+  <si>
+    <t>SM_Env_Plant_02</t>
+  </si>
+  <si>
+    <t>SM_Env_Plant_01</t>
+  </si>
+  <si>
+    <t>SM_Env_Plant_04</t>
+  </si>
+  <si>
+    <t>Rudy</t>
+  </si>
+  <si>
+    <t>3D model of rudy</t>
+  </si>
+  <si>
+    <t>Ea-nasir</t>
+  </si>
+  <si>
+    <t>3D model of ea-nasir</t>
+  </si>
+  <si>
+    <t>dunes</t>
+  </si>
+  <si>
+    <t>image of dunes level</t>
+  </si>
+  <si>
+    <t>labyrinth</t>
+  </si>
+  <si>
+    <t>image of labyrinth</t>
+  </si>
+  <si>
+    <t>wip</t>
+  </si>
+  <si>
+    <t>placeholder wip sign</t>
+  </si>
+  <si>
+    <t>blood splat</t>
+  </si>
+  <si>
+    <t>blood UI element</t>
+  </si>
+  <si>
+    <t>button (Shadow)</t>
+  </si>
+  <si>
+    <t>button and background UI element</t>
+  </si>
+  <si>
+    <t>rock Throw Crosshair</t>
+  </si>
+  <si>
+    <t>UI element for rock throw crosshair</t>
+  </si>
+  <si>
+    <t>ground raise crosshair</t>
+  </si>
+  <si>
+    <t>Ui Element for ground raise crosshair</t>
+  </si>
+  <si>
+    <t>Shoot Test</t>
+  </si>
+  <si>
+    <t>animation for testing shooting</t>
+  </si>
+  <si>
+    <t>FPS arms</t>
+  </si>
+  <si>
+    <t>player arms</t>
+  </si>
+  <si>
+    <t>3D model of Ea-nasor</t>
+  </si>
+  <si>
+    <t>SM_Env_Rock_Cliff_01</t>
+  </si>
+  <si>
+    <t>rock environment</t>
+  </si>
+  <si>
+    <t>SM_Env_Rock_Cliff_03</t>
+  </si>
+  <si>
+    <t>SM_Env_Rock_Cliff_02</t>
+  </si>
+  <si>
+    <t>SM_Env_Rock_Cliff_Arch_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SM_Env_Rock_Cliff_Arch_PIllar_01 </t>
+  </si>
+  <si>
+    <t>SM_Env_Rock_Cliff_Cut_01</t>
+  </si>
+  <si>
+    <t>SM_Env_Rock_Flat_02</t>
+  </si>
+  <si>
+    <t>SM_Env_Rock_Peak_02</t>
+  </si>
+  <si>
+    <t>SM_Env_Sand_05</t>
+  </si>
+  <si>
+    <t>sand environment</t>
+  </si>
+  <si>
+    <t>SM_Env_Sand_03</t>
+  </si>
+  <si>
+    <t>SM_Env_Sand_02</t>
+  </si>
+  <si>
+    <t>Plateau_desert_005</t>
+  </si>
+  <si>
+    <t>mountain environment</t>
+  </si>
+  <si>
+    <t>Plateau_desert_001</t>
+  </si>
+  <si>
+    <t>Mountain_desert_010</t>
+  </si>
+  <si>
+    <t>Mountain_desert_007</t>
+  </si>
+  <si>
+    <t>Mountain_desert_001</t>
+  </si>
+  <si>
+    <t>SM_Env_Rock_Cliff_Arch_02</t>
+  </si>
+  <si>
+    <t>Torch</t>
+  </si>
+  <si>
+    <t>Torch prop</t>
+  </si>
+  <si>
+    <t>fire03</t>
+  </si>
+  <si>
+    <t>fire particle for torch</t>
+  </si>
+  <si>
+    <t>ST_Env_Block_09</t>
+  </si>
+  <si>
+    <t>end door</t>
+  </si>
+  <si>
+    <t>ST_Env_Doorway_03</t>
+  </si>
+  <si>
+    <t>end door frame</t>
+  </si>
+  <si>
+    <t>rudy</t>
+  </si>
+  <si>
+    <t>With Love from vertex studio (21)</t>
+  </si>
+  <si>
+    <t>Background music</t>
+  </si>
+  <si>
+    <t>golem</t>
+  </si>
+  <si>
+    <t>enemy model</t>
+  </si>
+  <si>
+    <t>animations for golem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,16 +346,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -71,12 +376,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,32 +696,1154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F15681-5057-4854-A1AD-BB6A6AC3F409}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="6">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Documentation/Development/MediaAssetsList.xlsx
+++ b/Documentation/Development/MediaAssetsList.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30461751\Desktop\EarthShard\Documentation\Development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336329A6-6FB9-4293-B1F3-0D15A90F362F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5944448F-D8ED-41B0-AEF2-57E54C419F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40485" yWindow="1080" windowWidth="28545" windowHeight="18240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40740" yWindow="4785" windowWidth="28800" windowHeight="15435" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MainMenu" sheetId="1" r:id="rId1"/>
     <sheet name="Level1" sheetId="3" r:id="rId2"/>
+    <sheet name="Level2" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="121">
   <si>
     <t>Asset name</t>
   </si>
@@ -332,6 +333,63 @@
   </si>
   <si>
     <t>animations for golem</t>
+  </si>
+  <si>
+    <t>ST_Env_Wall_01</t>
+  </si>
+  <si>
+    <t>wall for labyrinth</t>
+  </si>
+  <si>
+    <t>ST_Env_Wall_Damaged_01</t>
+  </si>
+  <si>
+    <t>ST_Env_Wall_Damaged_02</t>
+  </si>
+  <si>
+    <t>ST_Env_Wall_Damaged_03</t>
+  </si>
+  <si>
+    <t>ST_Env_Ceiling_Hole_01</t>
+  </si>
+  <si>
+    <t>ST_Env_Ceiiling_01</t>
+  </si>
+  <si>
+    <t>ceiling for labyrinth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST_Env_Floor_03 </t>
+  </si>
+  <si>
+    <t>floor for labyrinth</t>
+  </si>
+  <si>
+    <t>ST_Env_Floor_04</t>
+  </si>
+  <si>
+    <t>door for labyrinth</t>
+  </si>
+  <si>
+    <t>ST_Prop_Gem_03</t>
+  </si>
+  <si>
+    <t>switch and end door asset</t>
+  </si>
+  <si>
+    <t>ST_Prop_Gem_01</t>
+  </si>
+  <si>
+    <t>ST_Prop_Button_01</t>
+  </si>
+  <si>
+    <t>switch asset</t>
+  </si>
+  <si>
+    <t>ha-waterheater</t>
+  </si>
+  <si>
+    <t>ambient track</t>
   </si>
 </sst>
 </file>
@@ -408,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -416,6 +474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1846,4 +1905,477 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5A9B91-B7C1-475B-9EB8-97D5746F546C}">
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>